--- a/class test/class test 11/Test Record.xlsx
+++ b/class test/class test 11/Test Record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 11/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="198" documentId="11_68DF1BED38F31E1694601FE51815821B40A2AD41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90B00B64-C424-4161-A724-CDB2AAAB68BE}"/>
+  <xr:revisionPtr revIDLastSave="247" documentId="11_68DF1BED38F31E1694601FE51815821B40A2AD41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0805FD52-B090-4792-BAA9-B263E6E916FD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="35">
   <si>
     <t>NAME</t>
   </si>
@@ -120,6 +120,12 @@
   </si>
   <si>
     <t>ch7</t>
+  </si>
+  <si>
+    <t>ch8</t>
+  </si>
+  <si>
+    <t>ch9</t>
   </si>
 </sst>
 </file>
@@ -183,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -193,6 +199,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -208,10 +215,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -536,14 +539,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="18.58203125" bestFit="1" customWidth="1"/>
     <col min="3" max="8" width="7.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -568,8 +571,14 @@
       <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
@@ -594,8 +603,14 @@
       <c r="I2" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J2" s="5">
+        <v>20</v>
+      </c>
+      <c r="K2" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
@@ -620,8 +635,14 @@
       <c r="I3" s="2">
         <v>46248</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J3" s="2">
+        <v>46273</v>
+      </c>
+      <c r="K3" s="2">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -649,8 +670,14 @@
       <c r="I4" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -678,8 +705,14 @@
       <c r="I5" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J5" s="5">
+        <v>14</v>
+      </c>
+      <c r="K5" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -707,8 +740,14 @@
       <c r="I6" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J6" s="5">
+        <v>7</v>
+      </c>
+      <c r="K6" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4</v>
       </c>
@@ -736,8 +775,14 @@
       <c r="I7" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>5</v>
       </c>
@@ -765,8 +810,14 @@
       <c r="I8" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J8" s="5">
+        <v>16</v>
+      </c>
+      <c r="K8" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>6</v>
       </c>
@@ -794,8 +845,14 @@
       <c r="I9" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J9" s="5">
+        <v>4</v>
+      </c>
+      <c r="K9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>7</v>
       </c>
@@ -823,8 +880,14 @@
       <c r="I10" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J10" s="5">
+        <v>2</v>
+      </c>
+      <c r="K10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>8</v>
       </c>
@@ -849,9 +912,17 @@
       <c r="H11" s="1">
         <v>10</v>
       </c>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="5">
+        <v>10</v>
+      </c>
+      <c r="K11" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>9</v>
       </c>
@@ -879,8 +950,14 @@
       <c r="I12" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J12" s="5">
+        <v>4</v>
+      </c>
+      <c r="K12" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>10</v>
       </c>
@@ -908,8 +985,14 @@
       <c r="I13" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J13" s="5">
+        <v>16</v>
+      </c>
+      <c r="K13" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>11</v>
       </c>
@@ -937,8 +1020,14 @@
       <c r="I14" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J14" s="1">
+        <v>4</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>12</v>
       </c>
@@ -966,8 +1055,14 @@
       <c r="I15" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J15" s="5">
+        <v>4</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>13</v>
       </c>
@@ -995,8 +1090,14 @@
       <c r="I16" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1024,8 +1125,14 @@
       <c r="I17" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J17" s="5">
+        <v>14</v>
+      </c>
+      <c r="K17" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1053,8 +1160,14 @@
       <c r="I18" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J18" s="5">
+        <v>10</v>
+      </c>
+      <c r="K18" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1082,8 +1195,14 @@
       <c r="I19" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1111,8 +1230,14 @@
       <c r="I20" s="1">
         <v>13</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J20" s="5">
+        <v>16</v>
+      </c>
+      <c r="K20" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1137,9 +1262,17 @@
       <c r="H21" s="1">
         <v>16</v>
       </c>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="5">
+        <v>8</v>
+      </c>
+      <c r="K21" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1167,8 +1300,14 @@
       <c r="I22" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J22" s="5">
+        <v>7</v>
+      </c>
+      <c r="K22" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1194,6 +1333,12 @@
         <v>18</v>
       </c>
       <c r="I23" s="1">
+        <v>6</v>
+      </c>
+      <c r="J23" s="5">
+        <v>9</v>
+      </c>
+      <c r="K23" s="5">
         <v>6</v>
       </c>
     </row>
